--- a/research/traditional_assets/database/data/luxembourg/luxembourg_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_auto_truck.xlsx
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="K2">
-        <v>-1256.7</v>
+        <v>-46.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>194.8</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.913555992141454</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-4.207343412526998</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,76 +609,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>194.8</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>441.2</v>
+        <v>512.6</v>
       </c>
       <c r="V2">
-        <v>0.09041354153858765</v>
+        <v>5.035363457760314</v>
       </c>
       <c r="W2">
-        <v>-6.418283963227783</v>
+        <v>-0.05036440770151202</v>
       </c>
       <c r="X2">
-        <v>0.06071618103747273</v>
+        <v>0.2736179353605774</v>
       </c>
       <c r="Y2">
-        <v>-6.479000144265256</v>
+        <v>-0.3239823430620895</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-1.078715691351631</v>
+        <v>-0.546669140842457</v>
       </c>
       <c r="AB2">
-        <v>0.05935828731022397</v>
+        <v>0.09244242291916209</v>
       </c>
       <c r="AC2">
-        <v>-1.138073978661855</v>
+        <v>-0.639111563761619</v>
       </c>
       <c r="AD2">
-        <v>172.7</v>
+        <v>381.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>172.7</v>
+        <v>381.8</v>
       </c>
       <c r="AG2">
-        <v>-268.5</v>
+        <v>-130.8</v>
       </c>
       <c r="AH2">
-        <v>0.03418109846610588</v>
+        <v>0.7894954507857733</v>
       </c>
       <c r="AI2">
-        <v>0.1531028368794326</v>
+        <v>0.2678170594837262</v>
       </c>
       <c r="AJ2">
-        <v>-0.05822653047947433</v>
+        <v>4.510344827586205</v>
       </c>
       <c r="AK2">
-        <v>-0.3909435061153174</v>
+        <v>-0.1432639649507119</v>
       </c>
       <c r="AL2">
-        <v>8.699999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="AM2">
-        <v>-5.600000000000001</v>
+        <v>11.57</v>
       </c>
       <c r="AN2">
-        <v>-0.8788804071246819</v>
+        <v>-1.35486160397445</v>
       </c>
       <c r="AO2">
-        <v>-23.94252873563219</v>
+        <v>-16.45810055865922</v>
       </c>
       <c r="AP2">
-        <v>1.366412213740458</v>
+        <v>0.4641589779985806</v>
       </c>
       <c r="AQ2">
-        <v>37.19642857142856</v>
+        <v>-25.46240276577356</v>
       </c>
     </row>
     <row r="3">
@@ -698,16 +701,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1256.7</v>
+        <v>-46.3</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>194.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>1.913555992141454</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-4.207343412526998</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -719,76 +722,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>194.8</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>441.2</v>
+        <v>512.6</v>
       </c>
       <c r="V3">
-        <v>0.09041354153858765</v>
+        <v>5.035363457760314</v>
       </c>
       <c r="W3">
-        <v>-6.418283963227783</v>
+        <v>-0.05036440770151202</v>
       </c>
       <c r="X3">
-        <v>0.06071618103747273</v>
+        <v>0.2736179353605774</v>
       </c>
       <c r="Y3">
-        <v>-6.479000144265256</v>
+        <v>-0.3239823430620895</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-1.078715691351631</v>
+        <v>-0.546669140842457</v>
       </c>
       <c r="AB3">
-        <v>0.05935828731022397</v>
+        <v>0.09244242291916209</v>
       </c>
       <c r="AC3">
-        <v>-1.138073978661855</v>
+        <v>-0.639111563761619</v>
       </c>
       <c r="AD3">
-        <v>172.7</v>
+        <v>381.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>172.7</v>
+        <v>381.8</v>
       </c>
       <c r="AG3">
-        <v>-268.5</v>
+        <v>-130.8</v>
       </c>
       <c r="AH3">
-        <v>0.03418109846610588</v>
+        <v>0.7894954507857733</v>
       </c>
       <c r="AI3">
-        <v>0.1531028368794326</v>
+        <v>0.2678170594837262</v>
       </c>
       <c r="AJ3">
-        <v>-0.05822653047947433</v>
+        <v>4.510344827586205</v>
       </c>
       <c r="AK3">
-        <v>-0.3909435061153174</v>
+        <v>-0.1432639649507119</v>
       </c>
       <c r="AL3">
-        <v>8.699999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="AM3">
-        <v>-5.600000000000001</v>
+        <v>11.57</v>
       </c>
       <c r="AN3">
-        <v>-0.8788804071246819</v>
+        <v>-1.35486160397445</v>
       </c>
       <c r="AO3">
-        <v>-23.94252873563219</v>
+        <v>-16.45810055865922</v>
       </c>
       <c r="AP3">
-        <v>1.366412213740458</v>
+        <v>0.4641589779985806</v>
       </c>
       <c r="AQ3">
-        <v>37.19642857142856</v>
+        <v>-25.46240276577356</v>
       </c>
     </row>
   </sheetData>
